--- a/tests/data/test_scenarios/test_1/separate/test_bid_file2.xlsx
+++ b/tests/data/test_scenarios/test_1/separate/test_bid_file2.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PHWATES\OneDrive - kochind.com\Documents\Ad hoc\RFP Analysis Automation Files\OneDrive_2024-09-16\RFP Submissions\RFP data test\Dummy data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chrisw78\RFP Automation REPO\RFP_Analysis_Automation2\tests\data\test_scenarios\test_1\separate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75182F47-8E51-4938-AD62-BB7C7FA588A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93029B59-EA26-43C4-AC94-D040BBB48CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3225" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{87499309-8BB3-46FE-B956-E0DEEFF98C77}"/>
+    <workbookView xWindow="12555" yWindow="1290" windowWidth="25680" windowHeight="12360" xr2:uid="{87499309-8BB3-46FE-B956-E0DEEFF98C77}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="rebates" sheetId="2" r:id="rId2"/>
+    <sheet name="capacity" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
   <si>
     <t>Bid ID</t>
   </si>
@@ -56,9 +58,6 @@
     <t>Facility</t>
   </si>
   <si>
-    <t>Supplier 2</t>
-  </si>
-  <si>
     <t>Facility 1</t>
   </si>
   <si>
@@ -72,19 +71,68 @@
   </si>
   <si>
     <t>Facility 5</t>
+  </si>
+  <si>
+    <t>Amber</t>
+  </si>
+  <si>
+    <t>Supplier Name</t>
+  </si>
+  <si>
+    <t>Min Volume</t>
+  </si>
+  <si>
+    <t>Max Volume</t>
+  </si>
+  <si>
+    <t>Min Spend</t>
+  </si>
+  <si>
+    <t>Max Spend</t>
+  </si>
+  <si>
+    <t>% Rebate</t>
+  </si>
+  <si>
+    <t>$ Rebate</t>
+  </si>
+  <si>
+    <t>Pearl</t>
+  </si>
+  <si>
+    <t>Grouping</t>
+  </si>
+  <si>
+    <t>Capacity</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -110,9 +158,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -482,7 +541,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>3437457</v>
@@ -494,7 +553,7 @@
         <v>2.9684239536279827E-2</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -502,7 +561,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <v>3001110</v>
@@ -514,7 +573,7 @@
         <v>1.170383365317758</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -522,7 +581,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>24000</v>
@@ -534,7 +593,7 @@
         <v>0.80299446114729811</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -542,7 +601,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>357800</v>
@@ -554,7 +613,7 @@
         <v>1.4454421327541025</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -562,7 +621,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C6">
         <v>45000</v>
@@ -574,7 +633,127 @@
         <v>0.37582883593462929</v>
       </c>
       <c r="F6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="GUID" r:id="rId1"/>
+  </customProperties>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A87D580-5142-4D01-99E7-C6F93FE94ED5}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="B2" s="2">
+        <v>500</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1800</v>
+      </c>
+      <c r="D2" s="2">
+        <v>20000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>20001</v>
+      </c>
+      <c r="F2" s="3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="G2" s="4">
+        <v>42222</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1801</v>
+      </c>
+      <c r="C3" s="2">
+        <v>10000000000</v>
+      </c>
+      <c r="D3" s="2">
+        <v>21221</v>
+      </c>
+      <c r="E3" s="2">
+        <v>25000</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="G3" s="4">
+        <v>40202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="GUID" r:id="rId1"/>
+  </customProperties>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8F2AA90-5A22-4BAE-BBB5-4C149EE2C3C9}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>2000000</v>
       </c>
     </row>
   </sheetData>
